--- a/plantilla_importacion_clientes.xlsx
+++ b/plantilla_importacion_clientes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30416"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\USUARIO\Desktop\gestion-sistema-facturacion\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\OneDrive\Escritorio\gestion-sistema-facturacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BFB641B-E808-4CF9-89F6-99865CE27D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{9BFB641B-E808-4CF9-89F6-99865CE27D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD82C12B-6C70-4790-A549-B854F3202799}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E61CA428-5DBA-4E28-B2D3-D5708BFA31F4}"/>
   </bookViews>
@@ -29,15 +29,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="315">
   <si>
     <t>COLOR CELULAR</t>
   </si>
@@ -156,15 +153,9 @@
     <t>SWOVENRO</t>
   </si>
   <si>
-    <t>__CLAVE_SOL__</t>
-  </si>
-  <si>
     <t>INVERSIONES Y EDIFICACIONES JAPACAP SAC</t>
   </si>
   <si>
-    <t>987418822</t>
-  </si>
-  <si>
     <t>JAPACAP SAC</t>
   </si>
   <si>
@@ -180,9 +171,6 @@
     <t>https://japacapsac.cpe.webzary.pe/login</t>
   </si>
   <si>
-    <t>__CLAVE_SISTEMA__</t>
-  </si>
-  <si>
     <t>2025-11-01</t>
   </si>
   <si>
@@ -190,13 +178,827 @@
   </si>
   <si>
     <t>Producción</t>
+  </si>
+  <si>
+    <t>ruichiney</t>
+  </si>
+  <si>
+    <t>Lambayeque</t>
+  </si>
+  <si>
+    <t>Chiclayo</t>
+  </si>
+  <si>
+    <t>Rojo</t>
+  </si>
+  <si>
+    <t>73754029</t>
+  </si>
+  <si>
+    <t>Ger@l1995</t>
+  </si>
+  <si>
+    <t>HELAMAN DANNFERT GONZALES GAMARRA</t>
+  </si>
+  <si>
+    <t>922717723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OBSTMEDIC SAC </t>
+  </si>
+  <si>
+    <t>obstmedic.centro.medico@gmail.com</t>
+  </si>
+  <si>
+    <t>Plan Impulsa</t>
+  </si>
+  <si>
+    <t>https://obstmedic.miquipu.net/</t>
+  </si>
+  <si>
+    <t>20608439413</t>
+  </si>
+  <si>
+    <t>ROJO</t>
+  </si>
+  <si>
+    <t>Juarez Juarez Ramos Elver</t>
+  </si>
+  <si>
+    <t>JUAREZ JUAREZ RAMOS ELVER</t>
+  </si>
+  <si>
+    <t>Plan Emprende</t>
+  </si>
+  <si>
+    <t>https://juarezramos.miquipu.net/</t>
+  </si>
+  <si>
+    <t>ramoselver09@gmail.com</t>
+  </si>
+  <si>
+    <t>RUS</t>
+  </si>
+  <si>
+    <t>Concepcion Morocho Quillama</t>
+  </si>
+  <si>
+    <t>920 049 040</t>
+  </si>
+  <si>
+    <t>Chifa Ericka y Jessica</t>
+  </si>
+  <si>
+    <t>Malecon Checa 141 - Zarate - San Juan de Lurigancho</t>
+  </si>
+  <si>
+    <t>ericahm81@gmail.com</t>
+  </si>
+  <si>
+    <t>chifaerickayjessica.miquipu.net</t>
+  </si>
+  <si>
+    <t>VERDE</t>
+  </si>
+  <si>
+    <t>INTERNO</t>
+  </si>
+  <si>
+    <t>LAZARO RAMIREZ SICELA NANCY</t>
+  </si>
+  <si>
+    <t>SODA SOLANCH</t>
+  </si>
+  <si>
+    <t>sodasolanch.miquipu.net</t>
+  </si>
+  <si>
+    <t>AMARILLO</t>
+  </si>
+  <si>
+    <t>DELGADILLO MUÑOZ EDGAR</t>
+  </si>
+  <si>
+    <t>ESTILOS HOGAR</t>
+  </si>
+  <si>
+    <t>estiloshogar.miquipu.net</t>
+  </si>
+  <si>
+    <t>Barbara romani Rioja</t>
+  </si>
+  <si>
+    <t>LA CASA DE LOS COJINES</t>
+  </si>
+  <si>
+    <t>lacasadeloscojines@miquipu.net</t>
+  </si>
+  <si>
+    <t>lacasadeloscojines.miquipu.net</t>
+  </si>
+  <si>
+    <t>KENYIJHO</t>
+  </si>
+  <si>
+    <t>Ra75427570</t>
+  </si>
+  <si>
+    <t>RAMOS GARCIA KENYI JHOAN</t>
+  </si>
+  <si>
+    <t>JHOKEN IMPORT</t>
+  </si>
+  <si>
+    <t>ramsjhoan@gmail.com</t>
+  </si>
+  <si>
+    <t>vesticepe</t>
+  </si>
+  <si>
+    <t>VELASQUEZ TRANCA ARNOLD WILLIAM</t>
+  </si>
+  <si>
+    <t>942 138 935</t>
+  </si>
+  <si>
+    <t>MINIMARKET EL DRAGON</t>
+  </si>
+  <si>
+    <t>avelasquez1410@gmail.com</t>
+  </si>
+  <si>
+    <t>minimarketeldragon.miquipu.net</t>
+  </si>
+  <si>
+    <t>TOLEDO MARLY</t>
+  </si>
+  <si>
+    <t>904 517 094</t>
+  </si>
+  <si>
+    <t>TOLEDO VILLANUEVA MARLY YASMIN</t>
+  </si>
+  <si>
+    <t>yt6684197@gmail.com</t>
+  </si>
+  <si>
+    <t>toledomarly.miquipu.net</t>
+  </si>
+  <si>
+    <t>CARRASCO CARRASCO KLEIBER ADAIN</t>
+  </si>
+  <si>
+    <t>902 241 865</t>
+  </si>
+  <si>
+    <t>Kleicars motors</t>
+  </si>
+  <si>
+    <t>Kleibercarrasco2290@gmail.com</t>
+  </si>
+  <si>
+    <t>https://kleicarsmotors.miquipu.net/login</t>
+  </si>
+  <si>
+    <t>ESPECIAL</t>
+  </si>
+  <si>
+    <t>Lupita14</t>
+  </si>
+  <si>
+    <t>DISTRIBUIDORA MUNDO PELUDO SAC</t>
+  </si>
+  <si>
+    <t>Mundo Peludo</t>
+  </si>
+  <si>
+    <t>LIMA</t>
+  </si>
+  <si>
+    <t>LURIN</t>
+  </si>
+  <si>
+    <t>Av. san martin 580</t>
+  </si>
+  <si>
+    <t>distribuidoramundopeludo@gmail.com</t>
+  </si>
+  <si>
+    <t>https://mundopeludo.miquipu.net/dashboard</t>
+  </si>
+  <si>
+    <t>GENERAL</t>
+  </si>
+  <si>
+    <t>ENTORTIC</t>
+  </si>
+  <si>
+    <t>Wareentic</t>
+  </si>
+  <si>
+    <t>Maritza Edith Balvin Vilcapoma</t>
+  </si>
+  <si>
+    <t>Kumi kumi</t>
+  </si>
+  <si>
+    <t>EL AGUSTINO</t>
+  </si>
+  <si>
+    <t>Calle San Francisco 109</t>
+  </si>
+  <si>
+    <t>balvinvilcapoma@gmail.com</t>
+  </si>
+  <si>
+    <t>https://kumikumi.miquipu.net/login</t>
+  </si>
+  <si>
+    <t>Vasquez01</t>
+  </si>
+  <si>
+    <t>Lener hermiliano vasquez Aquino</t>
+  </si>
+  <si>
+    <t>Novedades L&amp;V Import</t>
+  </si>
+  <si>
+    <t>vasquezlener20@gmail.com</t>
+  </si>
+  <si>
+    <t>https://novedadeslvimport.miquipu.net/login</t>
+  </si>
+  <si>
+    <t>Martina1972Hs22</t>
+  </si>
+  <si>
+    <t>PERCY ANTONIO HIDALGO SANTIAGO</t>
+  </si>
+  <si>
+    <t>WUJIBYFAN</t>
+  </si>
+  <si>
+    <t>BARRANCA</t>
+  </si>
+  <si>
+    <t>PARAMONGA</t>
+  </si>
+  <si>
+    <t>OLIVAR MZ "U" LT 5 - PARAMONGA</t>
+  </si>
+  <si>
+    <t>:JEKARY22@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>https://wujibyfan.miquipu.net/login</t>
+  </si>
+  <si>
+    <t>BEGRANIC</t>
+  </si>
+  <si>
+    <t>nspillath</t>
+  </si>
+  <si>
+    <t>SPC MEDIC</t>
+  </si>
+  <si>
+    <t>CENTRO MÉDICO ESPECIALIZADO CHILCA SALUD</t>
+  </si>
+  <si>
+    <t>CAÑETE</t>
+  </si>
+  <si>
+    <t>CHILCA</t>
+  </si>
+  <si>
+    <t>apuertasf@gmail.com</t>
+  </si>
+  <si>
+    <t>https://chilcasalud.miquipu.net/login</t>
+  </si>
+  <si>
+    <t>Victor253023</t>
+  </si>
+  <si>
+    <t>SANCHEZ CHACCHI VICTOR ENRIQUE</t>
+  </si>
+  <si>
+    <t>LA CASA DE CASTI</t>
+  </si>
+  <si>
+    <t>: Marcavilca Jr. Sebastian de Luna #105 Chorrillos</t>
+  </si>
+  <si>
+    <t>lacasadecasti@gmail.com</t>
+  </si>
+  <si>
+    <t>https://lacasadecasti.cpe.webzary.pe/login</t>
+  </si>
+  <si>
+    <t>RUC 15</t>
+  </si>
+  <si>
+    <t>APTRINTU</t>
+  </si>
+  <si>
+    <t>26220578aA</t>
+  </si>
+  <si>
+    <t>RIVAS ALCALA CARLOS JOSE</t>
+  </si>
+  <si>
+    <t>Taller C&amp;R</t>
+  </si>
+  <si>
+    <t>Jr Piura 461 - HUANCAYO</t>
+  </si>
+  <si>
+    <t>Carlosalcalarivas2622@gmail.com</t>
+  </si>
+  <si>
+    <t>https://tallercr.cpe.webzary.pe/login</t>
+  </si>
+  <si>
+    <t>carlosalcalarivas2622@gmail.com</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">948 841 093 / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>912178855</t>
+    </r>
+  </si>
+  <si>
+    <t>11141601Fr</t>
+  </si>
+  <si>
+    <t>Joel Alexander Vela Portocarrero</t>
+  </si>
+  <si>
+    <t>Majo Grill</t>
+  </si>
+  <si>
+    <t>Urb. MARTINEZ DE CONPAGÑON H-17</t>
+  </si>
+  <si>
+    <t>joelvepo1601@gmail.com</t>
+  </si>
+  <si>
+    <t>https://majogrill.cpe.webzary.pe/login</t>
+  </si>
+  <si>
+    <t>Martin1977</t>
+  </si>
+  <si>
+    <t>Martín Walter Mamáni Paredes</t>
+  </si>
+  <si>
+    <t>Restaurante y Pollería</t>
+  </si>
+  <si>
+    <t>PUNO</t>
+  </si>
+  <si>
+    <t>AZANGARO</t>
+  </si>
+  <si>
+    <t>Av. Los próceres s/n</t>
+  </si>
+  <si>
+    <t>Martinwaltermamaniparedes@gmail.com</t>
+  </si>
+  <si>
+    <t>https://restauranteypolleria.cpe.webzary.pe/login</t>
+  </si>
+  <si>
+    <t>martinwaltermamaniparedes@gmail.com</t>
+  </si>
+  <si>
+    <t>CULIALLM</t>
+  </si>
+  <si>
+    <t>uebrister</t>
+  </si>
+  <si>
+    <t>GROUP KALE STORE E.I.R.L</t>
+  </si>
+  <si>
+    <t>GROUP KALE STORE</t>
+  </si>
+  <si>
+    <t>MZ O5 lote 26, los licenciados ventanilla</t>
+  </si>
+  <si>
+    <t>luis.r.q@hotmail.com</t>
+  </si>
+  <si>
+    <t>https://groupkalestore.cpe.webzary.pe/login</t>
+  </si>
+  <si>
+    <t>groUPKAE@#984</t>
+  </si>
+  <si>
+    <t>POLDENDW</t>
+  </si>
+  <si>
+    <t>Dalu2026</t>
+  </si>
+  <si>
+    <t>FABRICACIONES Y IMPORTACIONES DALU EIRL</t>
+  </si>
+  <si>
+    <t>DALU EIRL</t>
+  </si>
+  <si>
+    <t>Mza.B Lt 19 A.H los álamos Callao callao ventanilla</t>
+  </si>
+  <si>
+    <t>chavarriad635@gmail.com</t>
+  </si>
+  <si>
+    <t>https://dalu.cpe.webzary.pe/login</t>
+  </si>
+  <si>
+    <t>imporDAL@#2761</t>
+  </si>
+  <si>
+    <t>Saul17</t>
+  </si>
+  <si>
+    <t>ESPERANZA TV E.I.R.L.</t>
+  </si>
+  <si>
+    <t>916 054 663</t>
+  </si>
+  <si>
+    <t>esperanzatv.miquipu.net</t>
+  </si>
+  <si>
+    <t>LNAKDKLE</t>
+  </si>
+  <si>
+    <t>eUecAm6eb</t>
+  </si>
+  <si>
+    <t>José Luis Alvarado paucar</t>
+  </si>
+  <si>
+    <t>El BUEN PORTE</t>
+  </si>
+  <si>
+    <t>elbuenporte66@gmail.com</t>
+  </si>
+  <si>
+    <t>https://elbuenporte.miquipu.net/</t>
+  </si>
+  <si>
+    <t>Especial</t>
+  </si>
+  <si>
+    <t>Ramos12</t>
+  </si>
+  <si>
+    <t>Paraíso verde encantado</t>
+  </si>
+  <si>
+    <t>925 601 187</t>
+  </si>
+  <si>
+    <t>Caserío de nuevo Unión sin número Tingo María</t>
+  </si>
+  <si>
+    <t>leninramos1190@gmail.com</t>
+  </si>
+  <si>
+    <t>https://paraisoverdeencantado.cpe.webzary.pe/login</t>
+  </si>
+  <si>
+    <t>paraiSOV@#9489</t>
+  </si>
+  <si>
+    <t>Mype</t>
+  </si>
+  <si>
+    <t>Pariona12</t>
+  </si>
+  <si>
+    <t>Henrry Alfonso pariona pichiuza</t>
+  </si>
+  <si>
+    <t>976 352 802</t>
+  </si>
+  <si>
+    <t>Henry jeans</t>
+  </si>
+  <si>
+    <t>LOS OLIVOS</t>
+  </si>
+  <si>
+    <t>Mz 16a lote01 a.h Laura caller iberico</t>
+  </si>
+  <si>
+    <t>hpphenry88@gmail.com</t>
+  </si>
+  <si>
+    <t>https://henryjeans.cpe.webzary.pe/login</t>
+  </si>
+  <si>
+    <t>henrYJE@#1394</t>
+  </si>
+  <si>
+    <t>Dicava36*</t>
+  </si>
+  <si>
+    <t>Diana Carolina Castañeda Vargas</t>
+  </si>
+  <si>
+    <t>968 023 045</t>
+  </si>
+  <si>
+    <t>NOVUS CLEAN</t>
+  </si>
+  <si>
+    <t>JUNIN</t>
+  </si>
+  <si>
+    <t>HUANCAYO</t>
+  </si>
+  <si>
+    <t>Av. URUGUAY 960 - HUANCAYO</t>
+  </si>
+  <si>
+    <t>diancavargas434@gmail.com</t>
+  </si>
+  <si>
+    <t>https://novusclean.cpe.webzary.pe/login</t>
+  </si>
+  <si>
+    <t>novUSCL@#1249</t>
+  </si>
+  <si>
+    <t>David1010</t>
+  </si>
+  <si>
+    <t>Construferre Zuazu Eirl</t>
+  </si>
+  <si>
+    <t>Zuazu</t>
+  </si>
+  <si>
+    <t>COMAS</t>
+  </si>
+  <si>
+    <t>Jr. Jose de la Riva Aguero 249 San Agustín comas</t>
+  </si>
+  <si>
+    <t>construferrezuazu@gmail.com</t>
+  </si>
+  <si>
+    <t>https://zuazu.cpe.webzary.pe/login</t>
+  </si>
+  <si>
+    <t>zuaZU@#95030</t>
+  </si>
+  <si>
+    <t>Rus</t>
+  </si>
+  <si>
+    <t>MENRIDGE</t>
+  </si>
+  <si>
+    <t>wertwolav</t>
+  </si>
+  <si>
+    <t>Ederson Raúl loro rojas</t>
+  </si>
+  <si>
+    <t>La casa de los cojines</t>
+  </si>
+  <si>
+    <t>Jr Ricardo Herrera cercado de lima 499</t>
+  </si>
+  <si>
+    <t>edersonraul@gmail.com</t>
+  </si>
+  <si>
+    <t>MO262906ca</t>
+  </si>
+  <si>
+    <t>Mónica Pilar Quispe Taquila</t>
+  </si>
+  <si>
+    <t>SMK - Sumak</t>
+  </si>
+  <si>
+    <t>SAN JUAN DE MIRAFLORES</t>
+  </si>
+  <si>
+    <t>Filiberto Romero Mz K lt.13-A</t>
+  </si>
+  <si>
+    <t>monicapilar36@gmail.com</t>
+  </si>
+  <si>
+    <t>GERALDINE VICENTINA GONZALES GAMARRA</t>
+  </si>
+  <si>
+    <t>OBSTMEDIC SALUD INTEGRAL</t>
+  </si>
+  <si>
+    <t>JR. CASTILLA 260 - DISTRITO DE LURIN</t>
+  </si>
+  <si>
+    <t>obstmedicsedelurin@gmail.com</t>
+  </si>
+  <si>
+    <t>https://obstmedicsaludintegral.cpe.webzary.pe/login</t>
+  </si>
+  <si>
+    <t>obsRMED@#62165</t>
+  </si>
+  <si>
+    <t>verde</t>
+  </si>
+  <si>
+    <t>ODVadm2026</t>
+  </si>
+  <si>
+    <t>ARENADOS Y SERVICIOS GENERALES ODV INDUSTRIAL E.I.R.L.</t>
+  </si>
+  <si>
+    <t>979 829 786</t>
+  </si>
+  <si>
+    <t>ODV INDUSTRIAL</t>
+  </si>
+  <si>
+    <t>AV. NESTOR GAMBETTA MZA. D6 LOTE. 13 A.H. DANIEL ALCIDES CARRION (CARRET. NESTOR GAMBETA FRANJA RANSA COME) PROV. CONST. DEL CALLAO - PROV. CONST. DEL CALLAO - CALLAO</t>
+  </si>
+  <si>
+    <t>https://odvindustrial.cpe.webzary.pe/login</t>
+  </si>
+  <si>
+    <t>informes@odvindustrial.com</t>
+  </si>
+  <si>
+    <t>odviNDUS@#35654</t>
+  </si>
+  <si>
+    <t>M&amp;G INFRAESTRUCTURA Y SERVICIOS EIRL</t>
+  </si>
+  <si>
+    <t>AV. INAMBARI S/N KM. 0 OTR. MAZUCO (FRENTE AL GRIFO HOROSCOPO)</t>
+  </si>
+  <si>
+    <t>vickytagq2015@gmail.com</t>
+  </si>
+  <si>
+    <t>https://myginfraestructurayservicios.cpe.webzary.pe/login</t>
+  </si>
+  <si>
+    <t>mygINFRAES@#95953</t>
+  </si>
+  <si>
+    <t>MONTALVO SINCA LUCERO MARIANA</t>
+  </si>
+  <si>
+    <t>Vidrieria Santiago</t>
+  </si>
+  <si>
+    <t>Pampa km 110 - km 108</t>
+  </si>
+  <si>
+    <t>oscarmontalvo280178@gmail.com</t>
+  </si>
+  <si>
+    <t>https://vidrieriasantiago.cpe.webzary.pe/login</t>
+  </si>
+  <si>
+    <t>vidriERIASA@#58433</t>
+  </si>
+  <si>
+    <t>pbd3cF947i$</t>
+  </si>
+  <si>
+    <t>Makuña market</t>
+  </si>
+  <si>
+    <t>969646619 / 983 734 041</t>
+  </si>
+  <si>
+    <t>Makuña</t>
+  </si>
+  <si>
+    <t>Av.manuel prado 302 Junín</t>
+  </si>
+  <si>
+    <t>makunamarket@gmail.com</t>
+  </si>
+  <si>
+    <t>https://makunamarket.cpe.webzary.pe/login</t>
+  </si>
+  <si>
+    <t>makUNA@#45613</t>
+  </si>
+  <si>
+    <t>SOIR IMPORT E.I.R.L.</t>
+  </si>
+  <si>
+    <t>mz ñ lote 11 urb.san isidro ii etapa 3er piso</t>
+  </si>
+  <si>
+    <t>soir.import@gmail.com</t>
+  </si>
+  <si>
+    <t>http://soirimport.cpe.webzary.pe</t>
+  </si>
+  <si>
+    <t>TONNIMAS</t>
+  </si>
+  <si>
+    <t>misilynos</t>
+  </si>
+  <si>
+    <t>MANUFARMA E.I.R.L</t>
+  </si>
+  <si>
+    <t>MANUFARMA</t>
+  </si>
+  <si>
+    <t>HUANUCO</t>
+  </si>
+  <si>
+    <t>AMARILIS</t>
+  </si>
+  <si>
+    <t>HUANUCO - HUANUCO- AMARILIS</t>
+  </si>
+  <si>
+    <t>ortegarojasmary5@gmail.com</t>
+  </si>
+  <si>
+    <t>https://manufarma.cpe.webzary.pe/login</t>
+  </si>
+  <si>
+    <t>manuFARM@#9853</t>
+  </si>
+  <si>
+    <t>MYPE</t>
+  </si>
+  <si>
+    <t>especial</t>
+  </si>
+  <si>
+    <t>927982170</t>
+  </si>
+  <si>
+    <t>Plan Inicial</t>
+  </si>
+  <si>
+    <t>2025-07-01</t>
+  </si>
+  <si>
+    <t>2025-09-01</t>
+  </si>
+  <si>
+    <t>2025-10-01</t>
+  </si>
+  <si>
+    <t>2025-08-01</t>
+  </si>
+  <si>
+    <t>2026-01-01</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-04-01</t>
+  </si>
+  <si>
+    <t>2026-08-01</t>
+  </si>
+  <si>
+    <t>20512180354</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -208,6 +1010,28 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -236,18 +1060,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -264,9 +1091,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -304,7 +1131,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -410,7 +1237,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -552,7 +1379,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -560,38 +1387,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA90653D-8EB3-4852-92AE-A42A853FED1E}">
-  <dimension ref="A1:AK2"/>
+  <dimension ref="A1:AK38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="41.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="38.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="42.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="37.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="42.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="41.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="38.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="42.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="37.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="42.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="22.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="6" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="5" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="5" style="1" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="8.85546875" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="7.7109375" bestFit="1" customWidth="1"/>
@@ -729,53 +1556,61 @@
         <v>38</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="J2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="P2" s="3">
+        <v>59</v>
+      </c>
+      <c r="Q2" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="R2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T2" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P2" s="3">
-        <v>59</v>
-      </c>
-      <c r="Q2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="R2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="S2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="T2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>50</v>
-      </c>
+      <c r="W2" s="3"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="3"/>
       <c r="AA2" s="3">
         <v>59</v>
       </c>
       <c r="AB2" s="3">
         <v>59</v>
       </c>
+      <c r="AC2" s="3"/>
       <c r="AD2" s="3">
         <v>59</v>
       </c>
@@ -799,10 +1634,3165 @@
       </c>
       <c r="AK2" s="3">
         <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="1">
+        <v>20608439413</v>
+      </c>
+      <c r="D3" s="1">
+        <v>73754029</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="P3" s="3">
+        <v>39</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W3" s="3">
+        <v>39</v>
+      </c>
+      <c r="X3" s="3">
+        <v>39</v>
+      </c>
+      <c r="Y3" s="3">
+        <v>39</v>
+      </c>
+      <c r="Z3" s="3">
+        <v>39</v>
+      </c>
+      <c r="AA3" s="3">
+        <v>39</v>
+      </c>
+      <c r="AB3" s="3">
+        <v>39</v>
+      </c>
+      <c r="AC3" s="3"/>
+      <c r="AD3" s="3">
+        <v>39</v>
+      </c>
+      <c r="AE3" s="3">
+        <v>39</v>
+      </c>
+      <c r="AF3" s="3">
+        <v>39</v>
+      </c>
+      <c r="AG3" s="3">
+        <v>39</v>
+      </c>
+      <c r="AH3" s="3">
+        <v>39</v>
+      </c>
+      <c r="AI3" s="3">
+        <v>39</v>
+      </c>
+      <c r="AJ3" s="3">
+        <v>39</v>
+      </c>
+      <c r="AK3" s="3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="1">
+        <v>10449275051</v>
+      </c>
+      <c r="D4" s="1">
+        <v>44927505</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H4" s="1">
+        <v>997057825</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P4" s="3">
+        <v>29</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="S4" s="1">
+        <v>10449275051</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W4" s="3">
+        <v>29</v>
+      </c>
+      <c r="X4" s="3">
+        <v>29</v>
+      </c>
+      <c r="Y4" s="3">
+        <v>29</v>
+      </c>
+      <c r="Z4" s="3">
+        <v>29</v>
+      </c>
+      <c r="AA4" s="3">
+        <v>29</v>
+      </c>
+      <c r="AB4" s="3">
+        <v>29</v>
+      </c>
+      <c r="AC4" s="3"/>
+      <c r="AD4" s="3">
+        <v>29</v>
+      </c>
+      <c r="AE4" s="3">
+        <v>29</v>
+      </c>
+      <c r="AF4" s="3">
+        <v>29</v>
+      </c>
+      <c r="AG4" s="3">
+        <v>29</v>
+      </c>
+      <c r="AH4" s="3">
+        <v>29</v>
+      </c>
+      <c r="AI4" s="3">
+        <v>29</v>
+      </c>
+      <c r="AJ4" s="3">
+        <v>29</v>
+      </c>
+      <c r="AK4" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="1">
+        <v>10073457411</v>
+      </c>
+      <c r="D5" s="1">
+        <v>7345741</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P5" s="3">
+        <v>29</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="S5" s="1">
+        <v>10073457411</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W5" s="3">
+        <v>29</v>
+      </c>
+      <c r="X5" s="3">
+        <v>29</v>
+      </c>
+      <c r="Y5" s="3">
+        <v>29</v>
+      </c>
+      <c r="Z5" s="3">
+        <v>29</v>
+      </c>
+      <c r="AA5" s="3">
+        <v>29</v>
+      </c>
+      <c r="AB5" s="3">
+        <v>29</v>
+      </c>
+      <c r="AC5" s="3"/>
+      <c r="AD5" s="3">
+        <v>29</v>
+      </c>
+      <c r="AE5" s="3">
+        <v>29</v>
+      </c>
+      <c r="AF5" s="3">
+        <v>29</v>
+      </c>
+      <c r="AG5" s="3">
+        <v>29</v>
+      </c>
+      <c r="AH5" s="3">
+        <v>29</v>
+      </c>
+      <c r="AI5" s="3">
+        <v>29</v>
+      </c>
+      <c r="AJ5" s="3">
+        <v>29</v>
+      </c>
+      <c r="AK5" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="1">
+        <v>10454572471</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H6" s="1">
+        <v>997690975</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P6" s="3">
+        <v>29</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W6" s="3">
+        <v>29</v>
+      </c>
+      <c r="X6" s="3">
+        <v>29</v>
+      </c>
+      <c r="Y6" s="3">
+        <v>29</v>
+      </c>
+      <c r="Z6" s="3">
+        <v>29</v>
+      </c>
+      <c r="AA6" s="3">
+        <v>29</v>
+      </c>
+      <c r="AB6" s="3">
+        <v>29</v>
+      </c>
+      <c r="AC6" s="3"/>
+      <c r="AD6" s="3">
+        <v>29</v>
+      </c>
+      <c r="AE6" s="3">
+        <v>29</v>
+      </c>
+      <c r="AF6" s="3">
+        <v>29</v>
+      </c>
+      <c r="AG6" s="3">
+        <v>29</v>
+      </c>
+      <c r="AH6" s="3">
+        <v>29</v>
+      </c>
+      <c r="AI6" s="3">
+        <v>29</v>
+      </c>
+      <c r="AJ6" s="3">
+        <v>29</v>
+      </c>
+      <c r="AK6" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="1">
+        <v>10436464288</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H7" s="1">
+        <v>997842711</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P7" s="3">
+        <v>59</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W7" s="3"/>
+      <c r="X7" s="3">
+        <v>59</v>
+      </c>
+      <c r="Y7" s="3">
+        <v>59</v>
+      </c>
+      <c r="Z7" s="3">
+        <v>59</v>
+      </c>
+      <c r="AA7" s="3">
+        <v>59</v>
+      </c>
+      <c r="AB7" s="3">
+        <v>59</v>
+      </c>
+      <c r="AC7" s="3"/>
+      <c r="AD7" s="3">
+        <v>59</v>
+      </c>
+      <c r="AE7" s="3">
+        <v>59</v>
+      </c>
+      <c r="AF7" s="3">
+        <v>59</v>
+      </c>
+      <c r="AG7" s="3">
+        <v>59</v>
+      </c>
+      <c r="AH7" s="3">
+        <v>59</v>
+      </c>
+      <c r="AI7" s="3">
+        <v>59</v>
+      </c>
+      <c r="AJ7" s="3">
+        <v>59</v>
+      </c>
+      <c r="AK7" s="3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="1">
+        <v>10752390709</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H8" s="1">
+        <v>937041706</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="P8" s="3">
+        <v>19</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W8" s="3"/>
+      <c r="X8" s="3">
+        <v>19</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>19</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>19</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>19</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>19</v>
+      </c>
+      <c r="AC8" s="3"/>
+      <c r="AD8" s="3">
+        <v>19</v>
+      </c>
+      <c r="AE8" s="3">
+        <v>19</v>
+      </c>
+      <c r="AF8" s="3">
+        <v>19</v>
+      </c>
+      <c r="AG8" s="3">
+        <v>19</v>
+      </c>
+      <c r="AH8" s="3">
+        <v>19</v>
+      </c>
+      <c r="AI8" s="3">
+        <v>19</v>
+      </c>
+      <c r="AJ8" s="3">
+        <v>19</v>
+      </c>
+      <c r="AK8" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="1">
+        <v>10754275702</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H9" s="1">
+        <v>910547491</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P9" s="3">
+        <v>29</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W9" s="3"/>
+      <c r="X9" s="3"/>
+      <c r="Y9" s="3">
+        <v>29</v>
+      </c>
+      <c r="Z9" s="3">
+        <v>29</v>
+      </c>
+      <c r="AA9" s="3">
+        <v>29</v>
+      </c>
+      <c r="AB9" s="3">
+        <v>29</v>
+      </c>
+      <c r="AC9" s="3"/>
+      <c r="AD9" s="3">
+        <v>29</v>
+      </c>
+      <c r="AE9" s="3">
+        <v>29</v>
+      </c>
+      <c r="AF9" s="3">
+        <v>29</v>
+      </c>
+      <c r="AG9" s="3">
+        <v>29</v>
+      </c>
+      <c r="AH9" s="3">
+        <v>29</v>
+      </c>
+      <c r="AI9" s="3">
+        <v>29</v>
+      </c>
+      <c r="AJ9" s="3">
+        <v>29</v>
+      </c>
+      <c r="AK9" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" s="1">
+        <v>10702601041</v>
+      </c>
+      <c r="E10" s="1">
+        <v>70260104</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P10" s="3">
+        <v>29</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W10" s="3"/>
+      <c r="X10" s="3"/>
+      <c r="Y10" s="3">
+        <v>29</v>
+      </c>
+      <c r="Z10" s="3">
+        <v>29</v>
+      </c>
+      <c r="AA10" s="3">
+        <v>29</v>
+      </c>
+      <c r="AB10" s="3">
+        <v>29</v>
+      </c>
+      <c r="AC10" s="3"/>
+      <c r="AD10" s="3">
+        <v>29</v>
+      </c>
+      <c r="AE10" s="3">
+        <v>29</v>
+      </c>
+      <c r="AF10" s="3">
+        <v>29</v>
+      </c>
+      <c r="AG10" s="3">
+        <v>29</v>
+      </c>
+      <c r="AH10" s="3">
+        <v>29</v>
+      </c>
+      <c r="AI10" s="3">
+        <v>29</v>
+      </c>
+      <c r="AJ10" s="3">
+        <v>29</v>
+      </c>
+      <c r="AK10" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" s="1">
+        <v>10759603686</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="P11" s="3">
+        <v>19</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="U11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W11" s="3"/>
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3">
+        <v>19</v>
+      </c>
+      <c r="Z11" s="3">
+        <v>19</v>
+      </c>
+      <c r="AA11" s="3">
+        <v>19</v>
+      </c>
+      <c r="AB11" s="3">
+        <v>19</v>
+      </c>
+      <c r="AC11" s="3"/>
+      <c r="AD11" s="3">
+        <v>19</v>
+      </c>
+      <c r="AE11" s="3">
+        <v>19</v>
+      </c>
+      <c r="AF11" s="3">
+        <v>19</v>
+      </c>
+      <c r="AG11" s="3">
+        <v>19</v>
+      </c>
+      <c r="AH11" s="3">
+        <v>19</v>
+      </c>
+      <c r="AI11" s="3">
+        <v>19</v>
+      </c>
+      <c r="AJ11" s="3">
+        <v>19</v>
+      </c>
+      <c r="AK11" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" s="1">
+        <v>10462212548</v>
+      </c>
+      <c r="D12" s="1">
+        <v>46221254</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P12" s="3">
+        <v>29</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="T12" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="U12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W12" s="3"/>
+      <c r="X12" s="3"/>
+      <c r="Y12" s="3">
+        <v>29</v>
+      </c>
+      <c r="Z12" s="3">
+        <v>29</v>
+      </c>
+      <c r="AA12" s="3">
+        <v>29</v>
+      </c>
+      <c r="AB12" s="3">
+        <v>29</v>
+      </c>
+      <c r="AC12" s="3"/>
+      <c r="AD12" s="3">
+        <v>29</v>
+      </c>
+      <c r="AE12" s="3">
+        <v>29</v>
+      </c>
+      <c r="AF12" s="3">
+        <v>29</v>
+      </c>
+      <c r="AG12" s="3">
+        <v>29</v>
+      </c>
+      <c r="AH12" s="3">
+        <v>29</v>
+      </c>
+      <c r="AI12" s="3">
+        <v>29</v>
+      </c>
+      <c r="AJ12" s="3">
+        <v>29</v>
+      </c>
+      <c r="AK12" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C13" s="1">
+        <v>20614632144</v>
+      </c>
+      <c r="D13" s="1">
+        <v>70339399</v>
+      </c>
+      <c r="E13" s="1">
+        <v>70339399</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H13" s="1">
+        <v>944123854</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P13" s="3">
+        <v>29</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="U13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W13" s="3"/>
+      <c r="X13" s="3"/>
+      <c r="Y13" s="3">
+        <v>29</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>29</v>
+      </c>
+      <c r="AA13" s="3">
+        <v>29</v>
+      </c>
+      <c r="AB13" s="3">
+        <v>29</v>
+      </c>
+      <c r="AC13" s="3"/>
+      <c r="AD13" s="3">
+        <v>29</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>29</v>
+      </c>
+      <c r="AF13" s="3">
+        <v>29</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>29</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>29</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>29</v>
+      </c>
+      <c r="AJ13" s="3">
+        <v>29</v>
+      </c>
+      <c r="AK13" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C14" s="1">
+        <v>10448786752</v>
+      </c>
+      <c r="D14" s="1">
+        <v>44878675</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H14" s="1">
+        <v>971766500</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P14" s="3">
+        <v>29</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="U14" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V14" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W14" s="3"/>
+      <c r="X14" s="3"/>
+      <c r="Y14" s="3"/>
+      <c r="Z14" s="3">
+        <v>29</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>29</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>29</v>
+      </c>
+      <c r="AC14" s="3"/>
+      <c r="AD14" s="3">
+        <v>29</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>29</v>
+      </c>
+      <c r="AF14" s="3">
+        <v>29</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>29</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>29</v>
+      </c>
+      <c r="AI14" s="3">
+        <v>29</v>
+      </c>
+      <c r="AJ14" s="3">
+        <v>29</v>
+      </c>
+      <c r="AK14" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" s="1">
+        <v>10464029198</v>
+      </c>
+      <c r="D15" s="1">
+        <v>46402919</v>
+      </c>
+      <c r="E15" s="1">
+        <v>46402919</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H15" s="1">
+        <v>957190442</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="P15" s="3">
+        <v>19</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="U15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W15" s="3"/>
+      <c r="X15" s="3"/>
+      <c r="Y15" s="3"/>
+      <c r="Z15" s="3">
+        <v>19</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>19</v>
+      </c>
+      <c r="AB15" s="3">
+        <v>19</v>
+      </c>
+      <c r="AC15" s="3"/>
+      <c r="AD15" s="3">
+        <v>19</v>
+      </c>
+      <c r="AE15" s="3">
+        <v>19</v>
+      </c>
+      <c r="AF15" s="3">
+        <v>19</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>19</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>19</v>
+      </c>
+      <c r="AI15" s="3">
+        <v>19</v>
+      </c>
+      <c r="AJ15" s="3">
+        <v>19</v>
+      </c>
+      <c r="AK15" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" s="1">
+        <v>10158421637</v>
+      </c>
+      <c r="D16" s="1">
+        <v>15842163</v>
+      </c>
+      <c r="E16" s="1">
+        <v>15842163</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H16" s="1">
+        <v>986324631</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P16" s="3">
+        <v>29</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="U16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W16" s="3"/>
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3">
+        <v>29</v>
+      </c>
+      <c r="AA16" s="3">
+        <v>29</v>
+      </c>
+      <c r="AB16" s="3">
+        <v>29</v>
+      </c>
+      <c r="AC16" s="3"/>
+      <c r="AD16" s="3">
+        <v>29</v>
+      </c>
+      <c r="AE16" s="3">
+        <v>29</v>
+      </c>
+      <c r="AF16" s="3">
+        <v>29</v>
+      </c>
+      <c r="AG16" s="3">
+        <v>29</v>
+      </c>
+      <c r="AH16" s="3">
+        <v>29</v>
+      </c>
+      <c r="AI16" s="3">
+        <v>29</v>
+      </c>
+      <c r="AJ16" s="3">
+        <v>29</v>
+      </c>
+      <c r="AK16" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" s="1">
+        <v>20614350751</v>
+      </c>
+      <c r="D17" s="1">
+        <v>45275793</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H17" s="1">
+        <v>915252842</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="P17" s="3">
+        <v>59</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="T17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="U17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V17" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W17" s="3"/>
+      <c r="X17" s="3"/>
+      <c r="Y17" s="3"/>
+      <c r="Z17" s="3"/>
+      <c r="AA17" s="3">
+        <v>59</v>
+      </c>
+      <c r="AB17" s="3">
+        <v>59</v>
+      </c>
+      <c r="AC17" s="3"/>
+      <c r="AD17" s="3">
+        <v>59</v>
+      </c>
+      <c r="AE17" s="3">
+        <v>59</v>
+      </c>
+      <c r="AF17" s="3">
+        <v>59</v>
+      </c>
+      <c r="AG17" s="3">
+        <v>59</v>
+      </c>
+      <c r="AH17" s="3">
+        <v>59</v>
+      </c>
+      <c r="AI17" s="3">
+        <v>59</v>
+      </c>
+      <c r="AJ17" s="3">
+        <v>59</v>
+      </c>
+      <c r="AK17" s="3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18" s="1">
+        <v>10094889010</v>
+      </c>
+      <c r="D18" s="1">
+        <v>9488901</v>
+      </c>
+      <c r="E18" s="1">
+        <v>9488901</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="P18" s="3">
+        <v>19</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="S18" s="1">
+        <v>10094889010</v>
+      </c>
+      <c r="T18" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="U18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W18" s="3"/>
+      <c r="X18" s="3"/>
+      <c r="Y18" s="3"/>
+      <c r="Z18" s="3">
+        <v>19</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>19</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>19</v>
+      </c>
+      <c r="AC18" s="3"/>
+      <c r="AD18" s="3">
+        <v>19</v>
+      </c>
+      <c r="AE18" s="3">
+        <v>19</v>
+      </c>
+      <c r="AF18" s="3">
+        <v>19</v>
+      </c>
+      <c r="AG18" s="3">
+        <v>19</v>
+      </c>
+      <c r="AH18" s="3">
+        <v>19</v>
+      </c>
+      <c r="AI18" s="3">
+        <v>19</v>
+      </c>
+      <c r="AJ18" s="3">
+        <v>19</v>
+      </c>
+      <c r="AK18" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C19" s="1">
+        <v>15614811363</v>
+      </c>
+      <c r="D19" s="1">
+        <v>7996311</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="P19" s="3">
+        <v>59</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="S19" s="1">
+        <v>15614811363</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="U19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V19" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W19" s="3"/>
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3">
+        <v>59</v>
+      </c>
+      <c r="AA19" s="3">
+        <v>59</v>
+      </c>
+      <c r="AB19" s="3">
+        <v>59</v>
+      </c>
+      <c r="AC19" s="3"/>
+      <c r="AD19" s="3">
+        <v>59</v>
+      </c>
+      <c r="AE19" s="3">
+        <v>59</v>
+      </c>
+      <c r="AF19" s="3">
+        <v>59</v>
+      </c>
+      <c r="AG19" s="3">
+        <v>59</v>
+      </c>
+      <c r="AH19" s="3">
+        <v>59</v>
+      </c>
+      <c r="AI19" s="3">
+        <v>59</v>
+      </c>
+      <c r="AJ19" s="3">
+        <v>59</v>
+      </c>
+      <c r="AK19" s="3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="1">
+        <v>10704658503</v>
+      </c>
+      <c r="D20" s="1">
+        <v>70465850</v>
+      </c>
+      <c r="E20" s="1">
+        <v>70465850</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="H20" s="1">
+        <v>999556790</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P20" s="3">
+        <v>29</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="S20" s="1">
+        <v>10704658503</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="U20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W20" s="3"/>
+      <c r="X20" s="3"/>
+      <c r="Y20" s="3"/>
+      <c r="Z20" s="3">
+        <v>29</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>29</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>29</v>
+      </c>
+      <c r="AC20" s="3"/>
+      <c r="AD20" s="3">
+        <v>29</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>29</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>29</v>
+      </c>
+      <c r="AG20" s="3">
+        <v>29</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>29</v>
+      </c>
+      <c r="AI20" s="3">
+        <v>29</v>
+      </c>
+      <c r="AJ20" s="3">
+        <v>29</v>
+      </c>
+      <c r="AK20" s="3"/>
+    </row>
+    <row r="21" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" s="1">
+        <v>10407302821</v>
+      </c>
+      <c r="D21" s="1">
+        <v>40730282</v>
+      </c>
+      <c r="E21" s="1">
+        <v>40730282</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="H21" s="1">
+        <v>951892715</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P21" s="3">
+        <v>29</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="S21" s="1">
+        <v>10407302821</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="U21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W21" s="3"/>
+      <c r="X21" s="3"/>
+      <c r="Y21" s="3"/>
+      <c r="Z21" s="3">
+        <v>29</v>
+      </c>
+      <c r="AA21" s="3">
+        <v>29</v>
+      </c>
+      <c r="AB21" s="3">
+        <v>29</v>
+      </c>
+      <c r="AC21" s="3"/>
+      <c r="AD21" s="3">
+        <v>29</v>
+      </c>
+      <c r="AE21" s="3">
+        <v>29</v>
+      </c>
+      <c r="AF21" s="3">
+        <v>29</v>
+      </c>
+      <c r="AG21" s="3">
+        <v>29</v>
+      </c>
+      <c r="AH21" s="3">
+        <v>29</v>
+      </c>
+      <c r="AI21" s="3">
+        <v>29</v>
+      </c>
+      <c r="AJ21" s="3">
+        <v>29</v>
+      </c>
+      <c r="AK21" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="1">
+        <v>20615368041</v>
+      </c>
+      <c r="D22" s="1">
+        <v>74135788</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="H22" s="1">
+        <v>939253807</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P22" s="3">
+        <v>29</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="U22" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V22" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W22" s="3"/>
+      <c r="X22" s="3"/>
+      <c r="Y22" s="3"/>
+      <c r="Z22" s="3">
+        <v>29</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>29</v>
+      </c>
+      <c r="AB22" s="3">
+        <v>29</v>
+      </c>
+      <c r="AC22" s="3"/>
+      <c r="AD22" s="3">
+        <v>29</v>
+      </c>
+      <c r="AE22" s="3">
+        <v>29</v>
+      </c>
+      <c r="AF22" s="3">
+        <v>29</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>29</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>29</v>
+      </c>
+      <c r="AI22" s="3">
+        <v>29</v>
+      </c>
+      <c r="AJ22" s="3">
+        <v>29</v>
+      </c>
+      <c r="AK22" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C23" s="1">
+        <v>20615087158</v>
+      </c>
+      <c r="D23" s="1">
+        <v>72325096</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="H23" s="1">
+        <v>949924443</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="P23" s="3">
+        <v>59</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="S23" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="T23" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="U23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V23" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W23" s="3"/>
+      <c r="X23" s="3"/>
+      <c r="Y23" s="3"/>
+      <c r="Z23" s="3"/>
+      <c r="AA23" s="3"/>
+      <c r="AB23" s="3"/>
+      <c r="AC23" s="3"/>
+      <c r="AD23" s="3">
+        <v>59</v>
+      </c>
+      <c r="AE23" s="3">
+        <v>59</v>
+      </c>
+      <c r="AF23" s="3">
+        <v>59</v>
+      </c>
+      <c r="AG23" s="3">
+        <v>59</v>
+      </c>
+      <c r="AH23" s="3">
+        <v>59</v>
+      </c>
+      <c r="AI23" s="3">
+        <v>59</v>
+      </c>
+      <c r="AJ23" s="3">
+        <v>59</v>
+      </c>
+      <c r="AK23" s="3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="1">
+        <v>20610435557</v>
+      </c>
+      <c r="E24" s="1">
+        <v>71341437</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P24" s="3">
+        <v>29</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="T24" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="U24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V24" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W24" s="3"/>
+      <c r="X24" s="3">
+        <v>29</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>29</v>
+      </c>
+      <c r="Z24" s="3"/>
+      <c r="AA24" s="3"/>
+      <c r="AB24" s="3"/>
+      <c r="AC24" s="3"/>
+      <c r="AD24" s="3"/>
+      <c r="AE24" s="3">
+        <v>29</v>
+      </c>
+      <c r="AF24" s="3">
+        <v>29</v>
+      </c>
+      <c r="AG24" s="3">
+        <v>29</v>
+      </c>
+      <c r="AH24" s="3">
+        <v>29</v>
+      </c>
+      <c r="AI24" s="3">
+        <v>29</v>
+      </c>
+      <c r="AJ24" s="3">
+        <v>29</v>
+      </c>
+      <c r="AK24" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="D25" s="1">
+        <v>9252166</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="H25" s="1">
+        <v>976611521</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P25" s="3">
+        <v>29</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="S25" s="1">
+        <v>20512180354</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="U25" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V25" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W25" s="3">
+        <v>29</v>
+      </c>
+      <c r="X25" s="3">
+        <v>29</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>29</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>29</v>
+      </c>
+      <c r="AA25" s="3">
+        <v>29</v>
+      </c>
+      <c r="AB25" s="3">
+        <v>29</v>
+      </c>
+      <c r="AC25" s="3"/>
+      <c r="AD25" s="3"/>
+      <c r="AE25" s="3"/>
+      <c r="AF25" s="3">
+        <v>29</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>29</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>29</v>
+      </c>
+      <c r="AI25" s="3">
+        <v>29</v>
+      </c>
+      <c r="AJ25" s="3">
+        <v>29</v>
+      </c>
+      <c r="AK25" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C26" s="1">
+        <v>20615059553</v>
+      </c>
+      <c r="D26" s="1">
+        <v>40074338</v>
+      </c>
+      <c r="E26" s="1">
+        <v>40074338</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="P26" s="3">
+        <v>19</v>
+      </c>
+      <c r="Q26" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="S26" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="T26" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="U26" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V26" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W26" s="3"/>
+      <c r="X26" s="3"/>
+      <c r="Y26" s="3"/>
+      <c r="Z26" s="3"/>
+      <c r="AA26" s="3"/>
+      <c r="AB26" s="3"/>
+      <c r="AC26" s="3"/>
+      <c r="AD26" s="3"/>
+      <c r="AE26" s="3"/>
+      <c r="AF26" s="3"/>
+      <c r="AG26" s="3"/>
+      <c r="AH26" s="3">
+        <v>19</v>
+      </c>
+      <c r="AI26" s="3">
+        <v>19</v>
+      </c>
+      <c r="AJ26" s="3">
+        <v>19</v>
+      </c>
+      <c r="AK26" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C27" s="1">
+        <v>10476208276</v>
+      </c>
+      <c r="D27" s="1">
+        <v>47620827</v>
+      </c>
+      <c r="E27" s="1">
+        <v>47620827</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="P27" s="3">
+        <v>59</v>
+      </c>
+      <c r="Q27" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="R27" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="S27" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="T27" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="U27" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V27" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W27" s="3"/>
+      <c r="X27" s="3"/>
+      <c r="Y27" s="3"/>
+      <c r="Z27" s="3"/>
+      <c r="AA27" s="3"/>
+      <c r="AB27" s="3"/>
+      <c r="AC27" s="3"/>
+      <c r="AD27" s="3"/>
+      <c r="AE27" s="3"/>
+      <c r="AF27" s="3"/>
+      <c r="AG27" s="3"/>
+      <c r="AH27" s="3">
+        <v>59</v>
+      </c>
+      <c r="AI27" s="3">
+        <v>59</v>
+      </c>
+      <c r="AJ27" s="3">
+        <v>59</v>
+      </c>
+      <c r="AK27" s="3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" s="1">
+        <v>10463190751</v>
+      </c>
+      <c r="D28" s="1">
+        <v>46319075</v>
+      </c>
+      <c r="E28" s="1">
+        <v>46319075</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="P28" s="3">
+        <v>19</v>
+      </c>
+      <c r="Q28" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="R28" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="S28" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="T28" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="U28" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V28" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W28" s="3"/>
+      <c r="X28" s="3"/>
+      <c r="Y28" s="3"/>
+      <c r="Z28" s="3"/>
+      <c r="AA28" s="3"/>
+      <c r="AB28" s="3"/>
+      <c r="AC28" s="3"/>
+      <c r="AD28" s="3"/>
+      <c r="AE28" s="3"/>
+      <c r="AF28" s="3"/>
+      <c r="AG28" s="3"/>
+      <c r="AH28" s="3">
+        <v>19</v>
+      </c>
+      <c r="AI28" s="3">
+        <v>19</v>
+      </c>
+      <c r="AJ28" s="3">
+        <v>19</v>
+      </c>
+      <c r="AK28" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C29" s="1">
+        <v>20610336591</v>
+      </c>
+      <c r="D29" s="1">
+        <v>45359142</v>
+      </c>
+      <c r="E29" s="1">
+        <v>45359142</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="H29" s="1">
+        <v>918362616</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="P29" s="3">
+        <v>19</v>
+      </c>
+      <c r="Q29" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="R29" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="S29" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="T29" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="U29" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V29" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W29" s="3"/>
+      <c r="X29" s="3"/>
+      <c r="Y29" s="3"/>
+      <c r="Z29" s="3"/>
+      <c r="AA29" s="3"/>
+      <c r="AB29" s="3"/>
+      <c r="AC29" s="3"/>
+      <c r="AD29" s="3"/>
+      <c r="AE29" s="3"/>
+      <c r="AF29" s="3"/>
+      <c r="AG29" s="3"/>
+      <c r="AH29" s="3">
+        <v>19</v>
+      </c>
+      <c r="AI29" s="3">
+        <v>19</v>
+      </c>
+      <c r="AJ29" s="3">
+        <v>19</v>
+      </c>
+      <c r="AK29" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C30" s="1">
+        <v>10753569087</v>
+      </c>
+      <c r="D30" s="1">
+        <v>75356908</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="H30" s="1">
+        <v>956391022</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="P30" s="3">
+        <v>19</v>
+      </c>
+      <c r="T30" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="U30" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V30" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W30" s="3"/>
+      <c r="X30" s="3"/>
+      <c r="Y30" s="3"/>
+      <c r="Z30" s="3"/>
+      <c r="AA30" s="3"/>
+      <c r="AB30" s="3"/>
+      <c r="AC30" s="3"/>
+      <c r="AD30" s="3"/>
+      <c r="AE30" s="3"/>
+      <c r="AF30" s="3"/>
+      <c r="AG30" s="3"/>
+      <c r="AH30" s="3"/>
+      <c r="AI30" s="3">
+        <v>19</v>
+      </c>
+      <c r="AJ30" s="3">
+        <v>19</v>
+      </c>
+      <c r="AK30" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C31" s="1">
+        <v>10425104735</v>
+      </c>
+      <c r="D31" s="1">
+        <v>42510473</v>
+      </c>
+      <c r="E31" s="1">
+        <v>42510473</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="H31" s="1">
+        <v>986848680</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="P31" s="3">
+        <v>19</v>
+      </c>
+      <c r="T31" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="U31" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V31" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W31" s="3"/>
+      <c r="X31" s="3"/>
+      <c r="Y31" s="3"/>
+      <c r="Z31" s="3"/>
+      <c r="AA31" s="3"/>
+      <c r="AB31" s="3"/>
+      <c r="AC31" s="3"/>
+      <c r="AD31" s="3"/>
+      <c r="AE31" s="3"/>
+      <c r="AF31" s="3"/>
+      <c r="AG31" s="3"/>
+      <c r="AH31" s="3"/>
+      <c r="AI31" s="3">
+        <v>19</v>
+      </c>
+      <c r="AJ31" s="3">
+        <v>19</v>
+      </c>
+      <c r="AK31" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C32" s="1">
+        <v>10749999271</v>
+      </c>
+      <c r="D32" s="1">
+        <v>74999927</v>
+      </c>
+      <c r="E32" s="1">
+        <v>74999927</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="H32" s="1">
+        <v>922717723</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P32" s="3">
+        <v>29</v>
+      </c>
+      <c r="Q32" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="R32" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="S32" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="T32" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="U32" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V32" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W32" s="3"/>
+      <c r="X32" s="3"/>
+      <c r="Y32" s="3"/>
+      <c r="Z32" s="3"/>
+      <c r="AA32" s="3"/>
+      <c r="AB32" s="3"/>
+      <c r="AC32" s="3"/>
+      <c r="AD32" s="3"/>
+      <c r="AE32" s="3"/>
+      <c r="AF32" s="3"/>
+      <c r="AG32" s="3"/>
+      <c r="AH32" s="3"/>
+      <c r="AI32" s="3">
+        <v>29</v>
+      </c>
+      <c r="AJ32" s="3">
+        <v>29</v>
+      </c>
+      <c r="AK32" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C33" s="1">
+        <v>20616023072</v>
+      </c>
+      <c r="D33" s="1">
+        <v>25766207</v>
+      </c>
+      <c r="E33" s="1">
+        <v>25766207</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="P33" s="3">
+        <v>59</v>
+      </c>
+      <c r="Q33" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="R33" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="S33" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="T33" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="U33" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V33" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W33" s="3"/>
+      <c r="X33" s="3"/>
+      <c r="Y33" s="3"/>
+      <c r="Z33" s="3"/>
+      <c r="AA33" s="3"/>
+      <c r="AB33" s="3"/>
+      <c r="AC33" s="3"/>
+      <c r="AD33" s="3"/>
+      <c r="AE33" s="3"/>
+      <c r="AF33" s="3"/>
+      <c r="AG33" s="3"/>
+      <c r="AH33" s="3"/>
+      <c r="AI33" s="3">
+        <v>59</v>
+      </c>
+      <c r="AJ33" s="3">
+        <v>59</v>
+      </c>
+      <c r="AK33" s="3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="34" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C34" s="1">
+        <v>20614969050</v>
+      </c>
+      <c r="D34" s="1">
+        <v>46144485</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F34" s="1">
+        <v>46144485</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="H34" s="1">
+        <v>913763898</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P34" s="3">
+        <v>29</v>
+      </c>
+      <c r="Q34" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="R34" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="S34" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="T34" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="U34" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V34" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W34" s="3"/>
+      <c r="X34" s="3"/>
+      <c r="Y34" s="3"/>
+      <c r="Z34" s="3"/>
+      <c r="AA34" s="3"/>
+      <c r="AB34" s="3"/>
+      <c r="AC34" s="3"/>
+      <c r="AD34" s="3"/>
+      <c r="AE34" s="3"/>
+      <c r="AF34" s="3"/>
+      <c r="AG34" s="3"/>
+      <c r="AH34" s="3"/>
+      <c r="AI34" s="3">
+        <v>29</v>
+      </c>
+      <c r="AJ34" s="3">
+        <v>29</v>
+      </c>
+      <c r="AK34" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C35" s="1">
+        <v>10762971611</v>
+      </c>
+      <c r="D35" s="1">
+        <v>76297161</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F35" s="1">
+        <v>76297161</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="H35" s="1">
+        <v>913763898</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P35" s="3">
+        <v>29</v>
+      </c>
+      <c r="Q35" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="R35" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="S35" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="T35" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="U35" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V35" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W35" s="3"/>
+      <c r="X35" s="3"/>
+      <c r="Y35" s="3"/>
+      <c r="Z35" s="3"/>
+      <c r="AA35" s="3"/>
+      <c r="AB35" s="3"/>
+      <c r="AC35" s="3"/>
+      <c r="AD35" s="3"/>
+      <c r="AE35" s="3"/>
+      <c r="AF35" s="3"/>
+      <c r="AG35" s="3"/>
+      <c r="AH35" s="3"/>
+      <c r="AI35" s="3">
+        <v>29</v>
+      </c>
+      <c r="AJ35" s="3">
+        <v>29</v>
+      </c>
+      <c r="AK35" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C36" s="1">
+        <v>20611528745</v>
+      </c>
+      <c r="D36" s="1">
+        <v>71420111</v>
+      </c>
+      <c r="E36" s="1">
+        <v>71420111</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="P36" s="3">
+        <v>19</v>
+      </c>
+      <c r="Q36" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="R36" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="S36" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="T36" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="U36" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V36" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W36" s="3"/>
+      <c r="X36" s="3"/>
+      <c r="Y36" s="3"/>
+      <c r="Z36" s="3"/>
+      <c r="AA36" s="3"/>
+      <c r="AB36" s="3"/>
+      <c r="AC36" s="3"/>
+      <c r="AD36" s="3"/>
+      <c r="AE36" s="3"/>
+      <c r="AF36" s="3"/>
+      <c r="AG36" s="3"/>
+      <c r="AH36" s="3"/>
+      <c r="AI36" s="3">
+        <v>19</v>
+      </c>
+      <c r="AJ36" s="3">
+        <v>19</v>
+      </c>
+      <c r="AK36" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C37" s="1">
+        <v>20613354949</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="H37" s="1">
+        <v>903289922</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P37" s="3">
+        <v>29</v>
+      </c>
+      <c r="Q37" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="T37" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="U37" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V37" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W37" s="3"/>
+      <c r="X37" s="3"/>
+      <c r="Y37" s="3"/>
+      <c r="Z37" s="3"/>
+      <c r="AA37" s="3"/>
+      <c r="AB37" s="3"/>
+      <c r="AC37" s="3"/>
+      <c r="AD37" s="3"/>
+      <c r="AE37" s="3"/>
+      <c r="AF37" s="3"/>
+      <c r="AG37" s="3">
+        <v>29</v>
+      </c>
+      <c r="AH37" s="3">
+        <v>29</v>
+      </c>
+      <c r="AI37" s="3">
+        <v>29</v>
+      </c>
+      <c r="AJ37" s="3">
+        <v>29</v>
+      </c>
+      <c r="AK37" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="38" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C38" s="1">
+        <v>20616050002</v>
+      </c>
+      <c r="D38" s="1">
+        <v>71609968</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="H38" s="1">
+        <v>917052556</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="P38" s="3">
+        <v>19</v>
+      </c>
+      <c r="Q38" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="R38" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="S38" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="T38" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="U38" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V38" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W38" s="3"/>
+      <c r="X38" s="3"/>
+      <c r="Y38" s="3"/>
+      <c r="Z38" s="3"/>
+      <c r="AA38" s="3"/>
+      <c r="AB38" s="3"/>
+      <c r="AC38" s="3"/>
+      <c r="AD38" s="3"/>
+      <c r="AE38" s="3"/>
+      <c r="AF38" s="3"/>
+      <c r="AG38" s="3"/>
+      <c r="AH38" s="3"/>
+      <c r="AI38" s="3"/>
+      <c r="AJ38" s="3"/>
+      <c r="AK38" s="3">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="F3" r:id="rId1" xr:uid="{DDB87A88-B7FA-4663-A42D-C29F3BCCD2B8}"/>
+    <hyperlink ref="N3" r:id="rId2" xr:uid="{7719F596-C751-4B04-9D78-5942530B6B10}"/>
+    <hyperlink ref="Q3" r:id="rId3" xr:uid="{B16CE553-1DBF-42D4-B339-2A4A37B86C05}"/>
+    <hyperlink ref="R3" r:id="rId4" xr:uid="{1FC6013B-87B7-4E03-8F85-62D8240A48F4}"/>
+    <hyperlink ref="Q4" r:id="rId5" xr:uid="{0160F190-C2D6-4A83-AAC1-246380B71192}"/>
+    <hyperlink ref="Q6" r:id="rId6" display="http://sodasolanch.miquipu.net/" xr:uid="{3D1D6186-73D1-4335-99B7-8D08AD286072}"/>
+    <hyperlink ref="Q7" r:id="rId7" display="http://estiloshogar.miquipu.net/" xr:uid="{E2006FF7-D1FF-4A35-ABB5-AD5272F89859}"/>
+    <hyperlink ref="Q11" r:id="rId8" display="http://toledomarly.miquipu.net/" xr:uid="{5525CE76-AFB4-4C90-9FAA-F81054721165}"/>
+    <hyperlink ref="Q12" r:id="rId9" xr:uid="{B70D3899-D21B-48EA-AD13-B4D528E47D56}"/>
+    <hyperlink ref="Q13" r:id="rId10" xr:uid="{49D8D8BF-6C05-4D37-AEEF-7169CA009825}"/>
+    <hyperlink ref="Q14" r:id="rId11" xr:uid="{7B80E4EA-73B8-4BDC-9F48-40F50EA8D9DB}"/>
+    <hyperlink ref="Q15" r:id="rId12" xr:uid="{6993F8EF-134C-4E4F-9E7D-E32D87219A3D}"/>
+    <hyperlink ref="Q16" r:id="rId13" xr:uid="{C1388496-96DD-48A3-AE86-30DA02AF4AF8}"/>
+    <hyperlink ref="Q17" r:id="rId14" xr:uid="{2DC0F5F2-CCBF-4DE4-A689-85F22B67EC49}"/>
+    <hyperlink ref="Q18" r:id="rId15" xr:uid="{95A1CC93-97FE-4B25-AD1C-32BA3EFBBAFD}"/>
+    <hyperlink ref="Q19" r:id="rId16" xr:uid="{64C44EA5-F5AB-4E0B-9980-ADCF71CA5466}"/>
+    <hyperlink ref="Q20" r:id="rId17" xr:uid="{0FE43289-D025-4095-8EC5-BD6E4D30BC8D}"/>
+    <hyperlink ref="Q21" r:id="rId18" xr:uid="{5880F212-7E95-423E-B880-9207B73AF524}"/>
+    <hyperlink ref="Q22" r:id="rId19" xr:uid="{D3CF152C-7059-4B26-BEBF-BF72C77E304F}"/>
+    <hyperlink ref="Q23" r:id="rId20" xr:uid="{D8E71C22-D8A9-42B7-91C3-368678A66FDE}"/>
+    <hyperlink ref="Q24" r:id="rId21" display="http://esperanzatv.miquipu.net/" xr:uid="{56659390-9BDE-4393-9E74-CFDFFB19E4CC}"/>
+    <hyperlink ref="Q25" r:id="rId22" xr:uid="{1266C2A7-68B6-41F2-9AE5-381891F45FB8}"/>
+    <hyperlink ref="Q26" r:id="rId23" xr:uid="{6F3AB35B-645F-48C7-8A24-2D599B81A813}"/>
+    <hyperlink ref="Q27" r:id="rId24" xr:uid="{9130B8B2-CE7F-4B71-9C09-AC81061A38EB}"/>
+    <hyperlink ref="Q28" r:id="rId25" xr:uid="{2D4DACE2-1A3B-4486-9819-DD906A2E29D9}"/>
+    <hyperlink ref="Q29" r:id="rId26" xr:uid="{EA19D2C3-EEF3-4AEC-8C75-AF1B192DFE6B}"/>
+    <hyperlink ref="Q32" r:id="rId27" xr:uid="{87E8D3C8-B917-44CA-A360-67FFE58571A0}"/>
+    <hyperlink ref="Q33" r:id="rId28" xr:uid="{FA77A9B4-980A-4878-BE6C-508E419497B7}"/>
+    <hyperlink ref="Q34" r:id="rId29" xr:uid="{C63A3B63-9EC2-4E57-A8E9-7C0895177DC2}"/>
+    <hyperlink ref="Q35" r:id="rId30" xr:uid="{6DB6A086-4F7E-4A2A-95AD-E01C23515E4C}"/>
+    <hyperlink ref="Q36" r:id="rId31" xr:uid="{8D421513-14CC-4C4E-9AD3-26289FC7AB67}"/>
+    <hyperlink ref="Q37" r:id="rId32" display="http://soirimport.cpe.webzary.pe/" xr:uid="{5C8DC92B-FC9F-4C34-BC93-EE9C68A486F9}"/>
+    <hyperlink ref="Q38" r:id="rId33" xr:uid="{65DC609D-DCC2-4D68-B17D-2D207DE85142}"/>
+    <hyperlink ref="Q2" r:id="rId34" xr:uid="{6FBFBE06-CC49-4C4A-8BD7-751DEF91F1C9}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId35"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="17" max="49" man="1"/>
+  </colBreaks>
 </worksheet>
 </file>